--- a/src/main/resources/excel/exceldata.xlsx
+++ b/src/main/resources/excel/exceldata.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\OneDrive\바탕 화면\"/>
     </mc:Choice>
@@ -16,10 +16,11 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet4" r:id="rId7" sheetId="4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="277">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="411" uniqueCount="281">
   <si>
     <t>company_id</t>
   </si>
@@ -901,12 +902,25 @@
   <si>
     <t>확인중</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>JSON</t>
+  </si>
+  <si>
+    <t>{"data":{"companyInfo":{"contents":{"defenseDesignationDate":"2022-08-29","businessNum":"608-17-31931","defenseRevenue":"","establishmentDate":"2008-06-10","civilianProducts":"2차전지 및 디스플레이 장비","companyZipCode":"52006","comClassification":"제조","companySize":"1","companyForm":"5","defenseProducts":"","homepageUrl":"","companyAddr2Ko":"","name":"정광산업기계","companyAddr1Ko":"경남 함안군 칠북면 북원로 272-80","companyMemberGubun":"G2","ceoName":"김정필","totalRevenue":"13610","productList":""}}}}</t>
+  </si>
+  <si>
+    <t>{"data":{"companyInfo":{"contents":{"defenseDesignationDate":"2025-01-09","businessNum":"620-84-59721","defenseRevenue":"","establishmentDate":"2021-08-03","civilianProducts":"","companyZipCode":"12982","comClassification":"무기 및 총포탄 제조업","companySize":"1","companyForm":"4","defenseProducts":"","homepageUrl":"","companyAddr2Ko":"","name":"주식회사에프원웍스","companyAddr1Ko":"경기 하남시 하남대로 947 (풍산동)","companyMemberGubun":"G2","ceoName":"박혜선","totalRevenue":"1089","productList":""}}}}</t>
+  </si>
+  <si>
+    <t>{"data":{"companyInfo":{"contents":{"defenseDesignationDate":"2021-07-06","businessNum":"139-81-08139","defenseRevenue":"","establishmentDate":"1992-07-01","civilianProducts":"소음, 진동, 충격 방지 제품","companyZipCode":"21691","comClassification":"제조업","companySize":"1","companyForm":"3","defenseProducts":"소음, 진동, 충격 방지 제품","homepageUrl":"http://www.nsv.co.kr","companyAddr2Ko":" NSV 사옥","name":"(주)엔에스브이","companyAddr1Ko":"인천 남동구 앵고개로 547 (고잔동)","companyMemberGubun":"G2","ceoName":"윤은중","totalRevenue":"28519","productList":""}}}}</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1302,346 +1316,346 @@
   <dimension ref="B2:CB5"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="26.75" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="16.25" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.25" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="42.25" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="23" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="24.125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="18.625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="21.875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="20.375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="22.375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="21.375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="18.125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="33" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="18.625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="69.75" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="24.375" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="19.75" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="16.25" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="16.125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="13.375" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="20.125" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="28.125" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="16" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="33" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="16.375" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="13.875" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="13.375" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="19" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="30" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="19.375" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="16.875" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="13.625" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="26.625" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="18.5" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="14.375" bestFit="1" customWidth="1"/>
-    <col min="42" max="45" width="14.75" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="17.625" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="21.625" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="23.625" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="14.375" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="17.75" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="18.625" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="25.375" bestFit="1" customWidth="1"/>
-    <col min="54" max="54" width="18.5" bestFit="1" customWidth="1"/>
-    <col min="55" max="55" width="22.25" bestFit="1" customWidth="1"/>
-    <col min="56" max="56" width="7.25" bestFit="1" customWidth="1"/>
-    <col min="57" max="57" width="10.125" bestFit="1" customWidth="1"/>
-    <col min="58" max="58" width="10.875" bestFit="1" customWidth="1"/>
-    <col min="59" max="59" width="7.25" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="28.75" bestFit="1" customWidth="1"/>
-    <col min="61" max="61" width="13.375" bestFit="1" customWidth="1"/>
-    <col min="62" max="62" width="25.625" bestFit="1" customWidth="1"/>
-    <col min="63" max="63" width="45.75" bestFit="1" customWidth="1"/>
-    <col min="64" max="64" width="31.5" bestFit="1" customWidth="1"/>
-    <col min="65" max="65" width="30.25" bestFit="1" customWidth="1"/>
-    <col min="66" max="67" width="15" bestFit="1" customWidth="1"/>
-    <col min="68" max="68" width="14.75" bestFit="1" customWidth="1"/>
-    <col min="69" max="69" width="20.75" bestFit="1" customWidth="1"/>
-    <col min="70" max="70" width="9.125" bestFit="1" customWidth="1"/>
-    <col min="71" max="71" width="14" bestFit="1" customWidth="1"/>
-    <col min="72" max="72" width="13.375" bestFit="1" customWidth="1"/>
-    <col min="73" max="73" width="20.625" bestFit="1" customWidth="1"/>
-    <col min="74" max="74" width="32.625" bestFit="1" customWidth="1"/>
-    <col min="75" max="75" width="26.5" bestFit="1" customWidth="1"/>
-    <col min="76" max="76" width="8.5" bestFit="1" customWidth="1"/>
-    <col min="77" max="78" width="27.875" bestFit="1" customWidth="1"/>
-    <col min="79" max="79" width="28.75" bestFit="1" customWidth="1"/>
-    <col min="80" max="80" width="25.625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="26.75"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="24.875"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="14.625"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="14.0"/>
+    <col min="6" max="7" bestFit="true" customWidth="true" width="16.25"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" width="19.25"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="42.25"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" width="23.0"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" width="24.125"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" width="18.625"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" width="21.875"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" width="20.375"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" width="22.375"/>
+    <col min="16" max="16" bestFit="true" customWidth="true" width="21.375"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" width="18.125"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" width="33.0"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" width="18.625"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" width="69.75"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" width="24.375"/>
+    <col min="22" max="22" bestFit="true" customWidth="true" width="19.75"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" width="16.25"/>
+    <col min="24" max="24" bestFit="true" customWidth="true" width="16.125"/>
+    <col min="25" max="25" bestFit="true" customWidth="true" width="13.375"/>
+    <col min="26" max="26" bestFit="true" customWidth="true" width="20.125"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" width="28.125"/>
+    <col min="28" max="28" bestFit="true" customWidth="true" width="16.0"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" width="33.0"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" width="16.375"/>
+    <col min="31" max="31" bestFit="true" customWidth="true" width="13.875"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" width="13.375"/>
+    <col min="33" max="33" bestFit="true" customWidth="true" width="19.0"/>
+    <col min="34" max="34" bestFit="true" customWidth="true" width="30.0"/>
+    <col min="35" max="35" bestFit="true" customWidth="true" width="19.375"/>
+    <col min="36" max="36" bestFit="true" customWidth="true" width="16.875"/>
+    <col min="37" max="37" bestFit="true" customWidth="true" width="13.625"/>
+    <col min="38" max="38" bestFit="true" customWidth="true" width="26.625"/>
+    <col min="39" max="39" bestFit="true" customWidth="true" width="18.5"/>
+    <col min="40" max="40" bestFit="true" customWidth="true" width="13.5"/>
+    <col min="41" max="41" bestFit="true" customWidth="true" width="14.375"/>
+    <col min="42" max="45" bestFit="true" customWidth="true" width="14.75"/>
+    <col min="46" max="46" bestFit="true" customWidth="true" width="17.625"/>
+    <col min="47" max="47" bestFit="true" customWidth="true" width="21.625"/>
+    <col min="48" max="48" bestFit="true" customWidth="true" width="23.625"/>
+    <col min="49" max="49" bestFit="true" customWidth="true" width="14.375"/>
+    <col min="50" max="50" bestFit="true" customWidth="true" width="12.5"/>
+    <col min="51" max="51" bestFit="true" customWidth="true" width="17.75"/>
+    <col min="52" max="52" bestFit="true" customWidth="true" width="18.625"/>
+    <col min="53" max="53" bestFit="true" customWidth="true" width="25.375"/>
+    <col min="54" max="54" bestFit="true" customWidth="true" width="18.5"/>
+    <col min="55" max="55" bestFit="true" customWidth="true" width="22.25"/>
+    <col min="56" max="56" bestFit="true" customWidth="true" width="7.25"/>
+    <col min="57" max="57" bestFit="true" customWidth="true" width="10.125"/>
+    <col min="58" max="58" bestFit="true" customWidth="true" width="10.875"/>
+    <col min="59" max="59" bestFit="true" customWidth="true" width="7.25"/>
+    <col min="60" max="60" bestFit="true" customWidth="true" width="28.75"/>
+    <col min="61" max="61" bestFit="true" customWidth="true" width="13.375"/>
+    <col min="62" max="62" bestFit="true" customWidth="true" width="25.625"/>
+    <col min="63" max="63" bestFit="true" customWidth="true" width="45.75"/>
+    <col min="64" max="64" bestFit="true" customWidth="true" width="31.5"/>
+    <col min="65" max="65" bestFit="true" customWidth="true" width="30.25"/>
+    <col min="66" max="67" bestFit="true" customWidth="true" width="15.0"/>
+    <col min="68" max="68" bestFit="true" customWidth="true" width="14.75"/>
+    <col min="69" max="69" bestFit="true" customWidth="true" width="20.75"/>
+    <col min="70" max="70" bestFit="true" customWidth="true" width="9.125"/>
+    <col min="71" max="71" bestFit="true" customWidth="true" width="14.0"/>
+    <col min="72" max="72" bestFit="true" customWidth="true" width="13.375"/>
+    <col min="73" max="73" bestFit="true" customWidth="true" width="20.625"/>
+    <col min="74" max="74" bestFit="true" customWidth="true" width="32.625"/>
+    <col min="75" max="75" bestFit="true" customWidth="true" width="26.5"/>
+    <col min="76" max="76" bestFit="true" customWidth="true" width="8.5"/>
+    <col min="77" max="78" bestFit="true" customWidth="true" width="27.875"/>
+    <col min="79" max="79" bestFit="true" customWidth="true" width="28.75"/>
+    <col min="80" max="80" bestFit="true" customWidth="true" width="25.625"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:80" x14ac:dyDescent="0.3">
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>0</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" t="s" s="0">
         <v>1</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" t="s" s="0">
         <v>2</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" t="s" s="0">
         <v>3</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" t="s" s="0">
         <v>4</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" t="s" s="0">
         <v>6</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="K2" t="s">
+      <c r="K2" t="s" s="0">
         <v>9</v>
       </c>
-      <c r="L2" t="s">
+      <c r="L2" t="s" s="0">
         <v>10</v>
       </c>
-      <c r="M2" t="s">
+      <c r="M2" t="s" s="0">
         <v>11</v>
       </c>
-      <c r="N2" t="s">
+      <c r="N2" t="s" s="0">
         <v>12</v>
       </c>
-      <c r="O2" t="s">
+      <c r="O2" t="s" s="0">
         <v>13</v>
       </c>
-      <c r="P2" t="s">
+      <c r="P2" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="Q2" t="s" s="0">
         <v>194</v>
       </c>
-      <c r="R2" t="s">
+      <c r="R2" t="s" s="0">
         <v>15</v>
       </c>
-      <c r="S2" t="s">
+      <c r="S2" t="s" s="0">
         <v>16</v>
       </c>
-      <c r="T2" t="s">
+      <c r="T2" t="s" s="0">
         <v>17</v>
       </c>
-      <c r="U2" t="s">
+      <c r="U2" t="s" s="0">
         <v>18</v>
       </c>
-      <c r="V2" t="s">
+      <c r="V2" t="s" s="0">
         <v>19</v>
       </c>
-      <c r="W2" t="s">
+      <c r="W2" t="s" s="0">
         <v>20</v>
       </c>
-      <c r="X2" t="s">
+      <c r="X2" t="s" s="0">
         <v>21</v>
       </c>
-      <c r="Y2" t="s">
+      <c r="Y2" t="s" s="0">
         <v>22</v>
       </c>
-      <c r="Z2" t="s">
+      <c r="Z2" t="s" s="0">
         <v>23</v>
       </c>
-      <c r="AA2" t="s">
+      <c r="AA2" t="s" s="0">
         <v>24</v>
       </c>
-      <c r="AB2" t="s">
+      <c r="AB2" t="s" s="0">
         <v>25</v>
       </c>
-      <c r="AC2" t="s">
+      <c r="AC2" t="s" s="0">
         <v>26</v>
       </c>
-      <c r="AD2" t="s">
+      <c r="AD2" t="s" s="0">
         <v>27</v>
       </c>
-      <c r="AE2" t="s">
+      <c r="AE2" t="s" s="0">
         <v>28</v>
       </c>
-      <c r="AF2" t="s">
+      <c r="AF2" t="s" s="0">
         <v>29</v>
       </c>
-      <c r="AG2" t="s">
+      <c r="AG2" t="s" s="0">
         <v>30</v>
       </c>
-      <c r="AH2" t="s">
+      <c r="AH2" t="s" s="0">
         <v>31</v>
       </c>
-      <c r="AI2" t="s">
+      <c r="AI2" t="s" s="0">
         <v>32</v>
       </c>
-      <c r="AJ2" t="s">
+      <c r="AJ2" t="s" s="0">
         <v>33</v>
       </c>
-      <c r="AK2" t="s">
+      <c r="AK2" t="s" s="0">
         <v>34</v>
       </c>
-      <c r="AL2" t="s">
+      <c r="AL2" t="s" s="0">
         <v>35</v>
       </c>
-      <c r="AM2" t="s">
+      <c r="AM2" t="s" s="0">
         <v>36</v>
       </c>
-      <c r="AN2" t="s">
+      <c r="AN2" t="s" s="0">
         <v>37</v>
       </c>
-      <c r="AO2" t="s">
+      <c r="AO2" t="s" s="0">
         <v>38</v>
       </c>
-      <c r="AP2" t="s">
+      <c r="AP2" t="s" s="0">
         <v>39</v>
       </c>
-      <c r="AQ2" t="s">
+      <c r="AQ2" t="s" s="0">
         <v>40</v>
       </c>
-      <c r="AR2" t="s">
+      <c r="AR2" t="s" s="0">
         <v>41</v>
       </c>
-      <c r="AS2" t="s">
+      <c r="AS2" t="s" s="0">
         <v>42</v>
       </c>
-      <c r="AT2" t="s">
+      <c r="AT2" t="s" s="0">
         <v>43</v>
       </c>
-      <c r="AU2" t="s">
+      <c r="AU2" t="s" s="0">
         <v>44</v>
       </c>
-      <c r="AV2" t="s">
+      <c r="AV2" t="s" s="0">
         <v>45</v>
       </c>
-      <c r="AW2" t="s">
+      <c r="AW2" t="s" s="0">
         <v>46</v>
       </c>
-      <c r="AX2" t="s">
+      <c r="AX2" t="s" s="0">
         <v>47</v>
       </c>
-      <c r="AY2" t="s">
+      <c r="AY2" t="s" s="0">
         <v>48</v>
       </c>
-      <c r="AZ2" t="s">
+      <c r="AZ2" t="s" s="0">
         <v>49</v>
       </c>
-      <c r="BA2" t="s">
+      <c r="BA2" t="s" s="0">
         <v>50</v>
       </c>
-      <c r="BB2" t="s">
+      <c r="BB2" t="s" s="0">
         <v>51</v>
       </c>
-      <c r="BC2" t="s">
+      <c r="BC2" t="s" s="0">
         <v>52</v>
       </c>
-      <c r="BD2" t="s">
+      <c r="BD2" t="s" s="0">
         <v>53</v>
       </c>
-      <c r="BE2" t="s">
+      <c r="BE2" t="s" s="0">
         <v>54</v>
       </c>
-      <c r="BF2" t="s">
+      <c r="BF2" t="s" s="0">
         <v>55</v>
       </c>
-      <c r="BG2" t="s">
+      <c r="BG2" t="s" s="0">
         <v>56</v>
       </c>
-      <c r="BH2" t="s">
+      <c r="BH2" t="s" s="0">
         <v>57</v>
       </c>
-      <c r="BI2" t="s">
+      <c r="BI2" t="s" s="0">
         <v>58</v>
       </c>
-      <c r="BJ2" t="s">
+      <c r="BJ2" t="s" s="0">
         <v>59</v>
       </c>
-      <c r="BK2" t="s">
+      <c r="BK2" t="s" s="0">
         <v>60</v>
       </c>
-      <c r="BL2" t="s">
+      <c r="BL2" t="s" s="0">
         <v>61</v>
       </c>
-      <c r="BM2" t="s">
+      <c r="BM2" t="s" s="0">
         <v>62</v>
       </c>
-      <c r="BN2" t="s">
+      <c r="BN2" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="BO2" t="s">
+      <c r="BO2" t="s" s="0">
         <v>64</v>
       </c>
-      <c r="BP2" t="s">
+      <c r="BP2" t="s" s="0">
         <v>65</v>
       </c>
-      <c r="BQ2" t="s">
+      <c r="BQ2" t="s" s="0">
         <v>66</v>
       </c>
-      <c r="BR2" t="s">
+      <c r="BR2" t="s" s="0">
         <v>67</v>
       </c>
-      <c r="BS2" t="s">
+      <c r="BS2" t="s" s="0">
         <v>68</v>
       </c>
-      <c r="BT2" t="s">
+      <c r="BT2" t="s" s="0">
         <v>69</v>
       </c>
-      <c r="BU2" t="s">
+      <c r="BU2" t="s" s="0">
         <v>70</v>
       </c>
-      <c r="BV2" t="s">
+      <c r="BV2" t="s" s="0">
         <v>71</v>
       </c>
-      <c r="BW2" t="s">
+      <c r="BW2" t="s" s="0">
         <v>72</v>
       </c>
-      <c r="BX2" t="s">
+      <c r="BX2" t="s" s="0">
         <v>73</v>
       </c>
-      <c r="BY2" t="s">
+      <c r="BY2" t="s" s="0">
         <v>74</v>
       </c>
-      <c r="BZ2" t="s">
+      <c r="BZ2" t="s" s="0">
         <v>75</v>
       </c>
-      <c r="CA2" t="s">
+      <c r="CA2" t="s" s="0">
         <v>76</v>
       </c>
-      <c r="CB2" t="s">
+      <c r="CB2" t="s" s="0">
         <v>77</v>
       </c>
     </row>
     <row r="3" spans="2:80" x14ac:dyDescent="0.3">
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>78</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" t="s" s="0">
         <v>79</v>
       </c>
-      <c r="D3" t="s">
-        <v>80</v>
-      </c>
-      <c r="E3">
+      <c r="D3" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="E3" s="0">
         <v>0</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" t="s" s="0">
         <v>81</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G3" t="s" s="0">
         <v>82</v>
       </c>
-      <c r="H3" t="s">
+      <c r="H3" t="s" s="0">
         <v>83</v>
       </c>
-      <c r="I3" t="s">
+      <c r="I3" t="s" s="0">
         <v>84</v>
       </c>
-      <c r="J3" t="s">
+      <c r="J3" t="s" s="0">
         <v>85</v>
       </c>
       <c r="L3" s="3">
@@ -1650,79 +1664,79 @@
       <c r="M3" s="1">
         <v>39609</v>
       </c>
-      <c r="N3" t="s">
-        <v>80</v>
-      </c>
-      <c r="O3" t="s">
-        <v>80</v>
-      </c>
-      <c r="P3" t="s">
+      <c r="N3" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="O3" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="P3" t="s" s="0">
         <v>86</v>
       </c>
-      <c r="Q3">
+      <c r="Q3" s="0">
         <v>52006</v>
       </c>
-      <c r="R3" t="s">
+      <c r="R3" t="s" s="0">
         <v>87</v>
       </c>
-      <c r="T3" t="s">
+      <c r="T3" t="s" s="0">
         <v>193</v>
       </c>
-      <c r="U3" t="s">
+      <c r="U3" t="s" s="0">
         <v>88</v>
       </c>
-      <c r="V3" t="s">
+      <c r="V3" t="s" s="0">
         <v>89</v>
       </c>
-      <c r="W3" t="s">
-        <v>80</v>
-      </c>
-      <c r="X3" t="s">
+      <c r="W3" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="X3" t="s" s="0">
         <v>90</v>
       </c>
-      <c r="Y3" t="s">
+      <c r="Y3" t="s" s="0">
         <v>91</v>
       </c>
-      <c r="AA3" t="s">
+      <c r="AA3" t="s" s="0">
         <v>92</v>
       </c>
-      <c r="AB3">
+      <c r="AB3" s="0">
         <v>52006</v>
       </c>
-      <c r="AC3" t="s">
+      <c r="AC3" t="s" s="0">
         <v>87</v>
       </c>
-      <c r="AD3" t="s">
+      <c r="AD3" t="s" s="0">
         <v>83</v>
       </c>
-      <c r="AE3" t="s">
+      <c r="AE3" t="s" s="0">
         <v>90</v>
       </c>
-      <c r="AF3" t="s">
+      <c r="AF3" t="s" s="0">
         <v>91</v>
       </c>
-      <c r="AG3">
+      <c r="AG3" s="0">
         <v>3139</v>
       </c>
-      <c r="AH3" t="s">
+      <c r="AH3" t="s" s="0">
         <v>93</v>
       </c>
-      <c r="AI3" t="s">
+      <c r="AI3" t="s" s="0">
         <v>94</v>
       </c>
-      <c r="AJ3" t="s">
+      <c r="AJ3" t="s" s="0">
         <v>95</v>
       </c>
-      <c r="AK3" t="s">
+      <c r="AK3" t="s" s="0">
         <v>96</v>
       </c>
-      <c r="AL3" t="s">
+      <c r="AL3" t="s" s="0">
         <v>97</v>
       </c>
-      <c r="AN3">
+      <c r="AN3" s="0">
         <v>1</v>
       </c>
-      <c r="AO3">
+      <c r="AO3" s="0">
         <v>5</v>
       </c>
       <c r="AP3" s="2">
@@ -1737,129 +1751,129 @@
       <c r="AS3" s="2">
         <v>1653</v>
       </c>
-      <c r="AT3">
+      <c r="AT3" s="0">
         <v>1</v>
       </c>
-      <c r="AU3" t="s">
+      <c r="AU3" t="s" s="0">
         <v>98</v>
       </c>
-      <c r="AV3" t="s">
-        <v>80</v>
-      </c>
-      <c r="AW3" t="s">
+      <c r="AV3" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="AW3" t="s" s="0">
         <v>99</v>
       </c>
-      <c r="AY3" t="s">
-        <v>80</v>
-      </c>
-      <c r="AZ3" t="s">
+      <c r="AY3" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="AZ3" t="s" s="0">
         <v>100</v>
       </c>
-      <c r="BA3" t="s">
-        <v>80</v>
-      </c>
-      <c r="BB3" t="s">
+      <c r="BA3" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="BB3" t="s" s="0">
         <v>101</v>
       </c>
-      <c r="BC3" t="s">
+      <c r="BC3" t="s" s="0">
         <v>98</v>
       </c>
       <c r="BD3" s="1">
         <v>44798.474343020833</v>
       </c>
-      <c r="BE3" t="s">
-        <v>80</v>
-      </c>
-      <c r="BF3" t="s">
+      <c r="BE3" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="BF3" t="s" s="0">
         <v>80</v>
       </c>
       <c r="BG3" s="1">
         <v>45670.49329421296</v>
       </c>
-      <c r="BH3" t="s">
+      <c r="BH3" t="s" s="0">
         <v>102</v>
       </c>
-      <c r="BI3" t="s">
+      <c r="BI3" t="s" s="0">
         <v>91</v>
       </c>
-      <c r="BJ3" t="s">
-        <v>80</v>
-      </c>
-      <c r="BK3" t="s">
+      <c r="BJ3" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="BK3" t="s" s="0">
         <v>103</v>
       </c>
-      <c r="BL3" t="s">
-        <v>80</v>
-      </c>
-      <c r="BM3" t="s">
+      <c r="BL3" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="BM3" t="s" s="0">
         <v>104</v>
       </c>
-      <c r="BN3" t="s">
+      <c r="BN3" t="s" s="0">
         <v>105</v>
       </c>
-      <c r="BO3" t="s">
+      <c r="BO3" t="s" s="0">
         <v>105</v>
       </c>
-      <c r="BP3" t="s">
-        <v>80</v>
-      </c>
-      <c r="BQ3" t="s">
-        <v>80</v>
-      </c>
-      <c r="BS3" t="s">
-        <v>80</v>
-      </c>
-      <c r="BU3" t="s">
-        <v>80</v>
-      </c>
-      <c r="BV3" t="s">
-        <v>80</v>
-      </c>
-      <c r="BW3" t="s">
-        <v>80</v>
-      </c>
-      <c r="BX3">
+      <c r="BP3" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="BQ3" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="BS3" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="BU3" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="BV3" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="BW3" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="BX3" s="0">
         <v>1137</v>
       </c>
-      <c r="BY3" t="s">
+      <c r="BY3" t="s" s="0">
         <v>98</v>
       </c>
-      <c r="BZ3">
+      <c r="BZ3" s="0">
         <v>0</v>
       </c>
-      <c r="CA3" t="s">
-        <v>80</v>
-      </c>
-      <c r="CB3" t="s">
+      <c r="CA3" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="CB3" t="s" s="0">
         <v>80</v>
       </c>
     </row>
     <row r="4" spans="2:80" x14ac:dyDescent="0.3">
-      <c r="B4" t="s">
+      <c r="B4" t="s" s="0">
         <v>106</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" t="s" s="0">
         <v>79</v>
       </c>
-      <c r="D4" t="s">
-        <v>80</v>
-      </c>
-      <c r="E4">
+      <c r="D4" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="E4" s="0">
         <v>0</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" t="s" s="0">
         <v>107</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4" t="s" s="0">
         <v>108</v>
       </c>
-      <c r="H4" t="s">
+      <c r="H4" t="s" s="0">
         <v>109</v>
       </c>
-      <c r="I4" t="s">
+      <c r="I4" t="s" s="0">
         <v>110</v>
       </c>
-      <c r="J4" t="s">
+      <c r="J4" t="s" s="0">
         <v>111</v>
       </c>
       <c r="L4" s="1">
@@ -1868,67 +1882,67 @@
       <c r="M4" s="1">
         <v>44411</v>
       </c>
-      <c r="N4" t="s">
-        <v>80</v>
-      </c>
-      <c r="O4" t="s">
-        <v>80</v>
-      </c>
-      <c r="P4" t="s">
+      <c r="N4" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="O4" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="P4" t="s" s="0">
         <v>112</v>
       </c>
-      <c r="Q4">
+      <c r="Q4" s="0">
         <v>12982</v>
       </c>
-      <c r="R4" t="s">
+      <c r="R4" t="s" s="0">
         <v>113</v>
       </c>
-      <c r="T4" t="s">
+      <c r="T4" t="s" s="0">
         <v>114</v>
       </c>
-      <c r="U4" t="s">
+      <c r="U4" t="s" s="0">
         <v>88</v>
       </c>
-      <c r="V4" t="s">
+      <c r="V4" t="s" s="0">
         <v>89</v>
       </c>
-      <c r="W4" t="s">
-        <v>80</v>
-      </c>
-      <c r="X4" t="s">
+      <c r="W4" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="X4" t="s" s="0">
         <v>115</v>
       </c>
-      <c r="Y4" t="s">
+      <c r="Y4" t="s" s="0">
         <v>116</v>
       </c>
-      <c r="AA4" t="s">
+      <c r="AA4" t="s" s="0">
         <v>117</v>
       </c>
-      <c r="AB4">
+      <c r="AB4" s="0">
         <v>12982</v>
       </c>
-      <c r="AC4" t="s">
+      <c r="AC4" t="s" s="0">
         <v>113</v>
       </c>
-      <c r="AE4" t="s">
+      <c r="AE4" t="s" s="0">
         <v>116</v>
       </c>
-      <c r="AF4" t="s">
+      <c r="AF4" t="s" s="0">
         <v>116</v>
       </c>
-      <c r="AJ4" t="s">
+      <c r="AJ4" t="s" s="0">
         <v>116</v>
       </c>
-      <c r="AK4" t="s">
+      <c r="AK4" t="s" s="0">
         <v>116</v>
       </c>
-      <c r="AN4">
+      <c r="AN4" s="0">
         <v>1</v>
       </c>
-      <c r="AO4">
+      <c r="AO4" s="0">
         <v>4</v>
       </c>
-      <c r="AP4">
+      <c r="AP4" s="0">
         <v>50</v>
       </c>
       <c r="AQ4" s="2">
@@ -1937,132 +1951,132 @@
       <c r="AR4" s="2">
         <v>1089</v>
       </c>
-      <c r="AS4">
+      <c r="AS4" s="0">
         <v>466</v>
       </c>
-      <c r="AT4" t="s">
+      <c r="AT4" t="s" s="0">
         <v>118</v>
       </c>
-      <c r="AU4" t="s">
+      <c r="AU4" t="s" s="0">
         <v>98</v>
       </c>
-      <c r="AV4" t="s">
-        <v>80</v>
-      </c>
-      <c r="AW4" t="s">
+      <c r="AV4" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="AW4" t="s" s="0">
         <v>99</v>
       </c>
-      <c r="AY4" t="s">
+      <c r="AY4" t="s" s="0">
         <v>119</v>
       </c>
-      <c r="AZ4" t="s">
+      <c r="AZ4" t="s" s="0">
         <v>120</v>
       </c>
-      <c r="BA4" t="s">
+      <c r="BA4" t="s" s="0">
         <v>121</v>
       </c>
-      <c r="BB4" t="s">
+      <c r="BB4" t="s" s="0">
         <v>122</v>
       </c>
-      <c r="BC4" t="s">
+      <c r="BC4" t="s" s="0">
         <v>98</v>
       </c>
       <c r="BD4" s="1">
         <v>45635.57964880787</v>
       </c>
-      <c r="BE4" t="s">
-        <v>80</v>
-      </c>
-      <c r="BF4" t="s">
+      <c r="BE4" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="BF4" t="s" s="0">
         <v>80</v>
       </c>
       <c r="BG4" s="1">
         <v>45667.466884687499</v>
       </c>
-      <c r="BH4" t="s">
+      <c r="BH4" t="s" s="0">
         <v>117</v>
       </c>
-      <c r="BI4" t="s">
+      <c r="BI4" t="s" s="0">
         <v>116</v>
       </c>
-      <c r="BJ4" t="s">
+      <c r="BJ4" t="s" s="0">
         <v>123</v>
       </c>
-      <c r="BK4" t="s">
+      <c r="BK4" t="s" s="0">
         <v>124</v>
       </c>
-      <c r="BL4" t="s">
+      <c r="BL4" t="s" s="0">
         <v>125</v>
       </c>
-      <c r="BM4" t="s">
+      <c r="BM4" t="s" s="0">
         <v>126</v>
       </c>
-      <c r="BN4" t="s">
+      <c r="BN4" t="s" s="0">
         <v>105</v>
       </c>
-      <c r="BO4" t="s">
+      <c r="BO4" t="s" s="0">
         <v>105</v>
       </c>
-      <c r="BP4" t="s">
-        <v>80</v>
-      </c>
-      <c r="BQ4" t="s">
-        <v>80</v>
-      </c>
-      <c r="BS4" t="s">
-        <v>80</v>
-      </c>
-      <c r="BU4" t="s">
-        <v>80</v>
-      </c>
-      <c r="BV4" t="s">
-        <v>80</v>
-      </c>
-      <c r="BW4" t="s">
-        <v>80</v>
-      </c>
-      <c r="BX4">
+      <c r="BP4" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="BQ4" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="BS4" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="BU4" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="BV4" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="BW4" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="BX4" s="0">
         <v>1366</v>
       </c>
-      <c r="BY4" t="s">
+      <c r="BY4" t="s" s="0">
         <v>127</v>
       </c>
-      <c r="BZ4">
+      <c r="BZ4" s="0">
         <v>0</v>
       </c>
-      <c r="CA4" t="s">
-        <v>80</v>
-      </c>
-      <c r="CB4" t="s">
+      <c r="CA4" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="CB4" t="s" s="0">
         <v>80</v>
       </c>
     </row>
     <row r="5" spans="2:80" x14ac:dyDescent="0.3">
-      <c r="B5" t="s">
+      <c r="B5" t="s" s="0">
         <v>128</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" t="s" s="0">
         <v>79</v>
       </c>
-      <c r="D5" t="s">
-        <v>80</v>
-      </c>
-      <c r="E5">
+      <c r="D5" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="E5" s="0">
         <v>0</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5" t="s" s="0">
         <v>129</v>
       </c>
-      <c r="G5" t="s">
+      <c r="G5" t="s" s="0">
         <v>130</v>
       </c>
-      <c r="H5" t="s">
+      <c r="H5" t="s" s="0">
         <v>131</v>
       </c>
-      <c r="I5" t="s">
+      <c r="I5" t="s" s="0">
         <v>132</v>
       </c>
-      <c r="J5" t="s">
+      <c r="J5" t="s" s="0">
         <v>133</v>
       </c>
       <c r="L5" s="1">
@@ -2071,88 +2085,88 @@
       <c r="M5" s="1">
         <v>33786</v>
       </c>
-      <c r="N5" t="s">
-        <v>80</v>
-      </c>
-      <c r="O5" t="s">
-        <v>80</v>
-      </c>
-      <c r="P5" t="s">
+      <c r="N5" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="O5" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="P5" t="s" s="0">
         <v>134</v>
       </c>
-      <c r="Q5">
+      <c r="Q5" s="0">
         <v>21691</v>
       </c>
-      <c r="R5" t="s">
+      <c r="R5" t="s" s="0">
         <v>135</v>
       </c>
-      <c r="S5" t="s">
+      <c r="S5" t="s" s="0">
         <v>136</v>
       </c>
-      <c r="T5" t="s">
+      <c r="T5" t="s" s="0">
         <v>137</v>
       </c>
-      <c r="U5" t="s">
+      <c r="U5" t="s" s="0">
         <v>88</v>
       </c>
-      <c r="V5" t="s">
+      <c r="V5" t="s" s="0">
         <v>89</v>
       </c>
-      <c r="W5" t="s">
-        <v>80</v>
-      </c>
-      <c r="X5" t="s">
+      <c r="W5" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="X5" t="s" s="0">
         <v>138</v>
       </c>
-      <c r="Y5" t="s">
+      <c r="Y5" t="s" s="0">
         <v>139</v>
       </c>
-      <c r="Z5" t="s">
+      <c r="Z5" t="s" s="0">
         <v>140</v>
       </c>
-      <c r="AA5" t="s">
+      <c r="AA5" t="s" s="0">
         <v>141</v>
       </c>
-      <c r="AB5">
+      <c r="AB5" s="0">
         <v>21691</v>
       </c>
-      <c r="AC5" t="s">
+      <c r="AC5" t="s" s="0">
         <v>135</v>
       </c>
-      <c r="AD5" t="s">
+      <c r="AD5" t="s" s="0">
         <v>142</v>
       </c>
-      <c r="AE5" t="s">
+      <c r="AE5" t="s" s="0">
         <v>138</v>
       </c>
-      <c r="AF5" t="s">
+      <c r="AF5" t="s" s="0">
         <v>139</v>
       </c>
-      <c r="AG5">
+      <c r="AG5" s="0">
         <v>6654</v>
       </c>
-      <c r="AH5" t="s">
+      <c r="AH5" t="s" s="0">
         <v>143</v>
       </c>
-      <c r="AI5" t="s">
+      <c r="AI5" t="s" s="0">
         <v>144</v>
       </c>
-      <c r="AJ5" t="s">
+      <c r="AJ5" t="s" s="0">
         <v>145</v>
       </c>
-      <c r="AK5" t="s">
+      <c r="AK5" t="s" s="0">
         <v>146</v>
       </c>
-      <c r="AL5" t="s">
+      <c r="AL5" t="s" s="0">
         <v>147</v>
       </c>
-      <c r="AM5" t="s">
+      <c r="AM5" t="s" s="0">
         <v>147</v>
       </c>
-      <c r="AN5">
+      <c r="AN5" s="0">
         <v>1</v>
       </c>
-      <c r="AO5">
+      <c r="AO5" s="0">
         <v>3</v>
       </c>
       <c r="AP5" s="2">
@@ -2167,100 +2181,100 @@
       <c r="AS5" s="2">
         <v>6508</v>
       </c>
-      <c r="AT5" t="s">
+      <c r="AT5" t="s" s="0">
         <v>148</v>
       </c>
-      <c r="AU5" t="s">
+      <c r="AU5" t="s" s="0">
         <v>98</v>
       </c>
       <c r="AV5" s="1">
         <v>45723.728573576387</v>
       </c>
-      <c r="AW5" t="s">
+      <c r="AW5" t="s" s="0">
         <v>99</v>
       </c>
-      <c r="AY5" t="s">
+      <c r="AY5" t="s" s="0">
         <v>149</v>
       </c>
-      <c r="AZ5" t="s">
+      <c r="AZ5" t="s" s="0">
         <v>150</v>
       </c>
-      <c r="BA5" t="s">
-        <v>80</v>
-      </c>
-      <c r="BB5" t="s">
+      <c r="BA5" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="BB5" t="s" s="0">
         <v>151</v>
       </c>
-      <c r="BC5" t="s">
+      <c r="BC5" t="s" s="0">
         <v>98</v>
       </c>
       <c r="BD5" s="1">
         <v>44370.453562499999</v>
       </c>
-      <c r="BE5" t="s">
-        <v>80</v>
-      </c>
-      <c r="BF5" t="s">
+      <c r="BE5" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="BF5" t="s" s="0">
         <v>152</v>
       </c>
       <c r="BG5" s="1">
         <v>45726.779027812503</v>
       </c>
-      <c r="BH5" t="s">
+      <c r="BH5" t="s" s="0">
         <v>153</v>
       </c>
-      <c r="BI5" t="s">
+      <c r="BI5" t="s" s="0">
         <v>146</v>
       </c>
-      <c r="BJ5" t="s">
+      <c r="BJ5" t="s" s="0">
         <v>154</v>
       </c>
-      <c r="BK5" t="s">
+      <c r="BK5" t="s" s="0">
         <v>155</v>
       </c>
-      <c r="BL5" t="s">
-        <v>80</v>
-      </c>
-      <c r="BM5" t="s">
+      <c r="BL5" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="BM5" t="s" s="0">
         <v>156</v>
       </c>
-      <c r="BN5" t="s">
-        <v>80</v>
-      </c>
-      <c r="BO5" t="s">
-        <v>80</v>
-      </c>
-      <c r="BP5" t="s">
+      <c r="BN5" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="BO5" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="BP5" t="s" s="0">
         <v>157</v>
       </c>
-      <c r="BQ5" t="s">
+      <c r="BQ5" t="s" s="0">
         <v>156</v>
       </c>
-      <c r="BS5" t="s">
-        <v>80</v>
-      </c>
-      <c r="BU5" t="s">
-        <v>80</v>
-      </c>
-      <c r="BV5" t="s">
-        <v>80</v>
-      </c>
-      <c r="BW5" t="s">
-        <v>80</v>
-      </c>
-      <c r="BX5">
+      <c r="BS5" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="BU5" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="BV5" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="BW5" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="BX5" s="0">
         <v>1041</v>
       </c>
-      <c r="BY5" t="s">
+      <c r="BY5" t="s" s="0">
         <v>127</v>
       </c>
-      <c r="BZ5">
+      <c r="BZ5" s="0">
         <v>0</v>
       </c>
-      <c r="CA5" t="s">
-        <v>80</v>
-      </c>
-      <c r="CB5" t="s">
+      <c r="CA5" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="CB5" t="s" s="0">
         <v>158</v>
       </c>
     </row>
@@ -2275,343 +2289,343 @@
   <dimension ref="B3:M55"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="16.25" customWidth="1"/>
-    <col min="3" max="3" width="14.5" customWidth="1"/>
-    <col min="4" max="4" width="15.625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="26.875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="29.375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" customWidth="true" width="16.25"/>
+    <col min="3" max="3" customWidth="true" width="14.5"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="15.625"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="26.875"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="29.375"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="7.875"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" width="10.875"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="14.625"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" width="13.875"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" width="11.375"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" width="11.125"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" width="14.375"/>
   </cols>
   <sheetData>
     <row r="3" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>159</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" t="s" s="0">
         <v>160</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" t="s" s="0">
         <v>161</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" t="s" s="0">
         <v>162</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" t="s" s="0">
         <v>163</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G3" t="s" s="0">
         <v>164</v>
       </c>
-      <c r="H3" t="s">
+      <c r="H3" t="s" s="0">
         <v>165</v>
       </c>
-      <c r="I3" t="s">
+      <c r="I3" t="s" s="0">
         <v>166</v>
       </c>
-      <c r="J3" t="s">
+      <c r="J3" t="s" s="0">
         <v>167</v>
       </c>
-      <c r="K3" t="s">
+      <c r="K3" t="s" s="0">
         <v>168</v>
       </c>
-      <c r="L3" t="s">
+      <c r="L3" t="s" s="0">
         <v>169</v>
       </c>
-      <c r="M3" t="s">
+      <c r="M3" t="s" s="0">
         <v>170</v>
       </c>
     </row>
     <row r="4" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B4" t="s">
+      <c r="B4" t="s" s="0">
         <v>171</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" t="s" s="0">
         <v>219</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" t="s" s="0">
         <v>172</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" t="s" s="0">
         <v>127</v>
       </c>
       <c r="F4" s="5">
         <v>1</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4" t="s" s="0">
         <v>98</v>
       </c>
-      <c r="H4" t="s">
+      <c r="H4" t="s" s="0">
         <v>173</v>
       </c>
-      <c r="I4" t="s">
+      <c r="I4" t="s" s="0">
         <v>174</v>
       </c>
       <c r="J4" s="1">
         <v>45992.681320983793</v>
       </c>
-      <c r="K4" t="s">
-        <v>80</v>
-      </c>
-      <c r="L4" t="s">
-        <v>80</v>
-      </c>
-      <c r="M4" t="s">
+      <c r="K4" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="L4" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="M4" t="s" s="0">
         <v>80</v>
       </c>
     </row>
     <row r="6" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B6" t="s">
+      <c r="B6" t="s" s="0">
         <v>160</v>
       </c>
     </row>
     <row r="7" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B7" t="s">
+      <c r="B7" t="s" s="0">
         <v>175</v>
       </c>
     </row>
     <row r="8" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B8" t="s">
+      <c r="B8" t="s" s="0">
         <v>176</v>
       </c>
     </row>
     <row r="9" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B9" t="s">
+      <c r="B9" t="s" s="0">
         <v>177</v>
       </c>
     </row>
     <row r="10" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B10" t="s">
+      <c r="B10" t="s" s="0">
         <v>178</v>
       </c>
     </row>
     <row r="11" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B11" t="s">
+      <c r="B11" t="s" s="0">
         <v>183</v>
       </c>
     </row>
     <row r="12" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B12" t="s">
+      <c r="B12" t="s" s="0">
         <v>180</v>
       </c>
     </row>
     <row r="13" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B13" t="s">
+      <c r="B13" t="s" s="0">
         <v>220</v>
       </c>
     </row>
     <row r="14" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B14" t="s">
+      <c r="B14" t="s" s="0">
         <v>221</v>
       </c>
     </row>
     <row r="15" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B15" t="s">
+      <c r="B15" t="s" s="0">
         <v>266</v>
       </c>
     </row>
     <row r="16" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B16" t="s">
+      <c r="B16" t="s" s="0">
         <v>222</v>
       </c>
     </row>
     <row r="17" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B17" t="s">
+      <c r="B17" t="s" s="0">
         <v>181</v>
       </c>
     </row>
     <row r="18" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B18" t="s">
+      <c r="B18" t="s" s="0">
         <v>182</v>
       </c>
     </row>
     <row r="19" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B19" t="s">
+      <c r="B19" t="s" s="0">
         <v>185</v>
       </c>
     </row>
     <row r="20" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B20" t="s">
+      <c r="B20" t="s" s="0">
         <v>223</v>
       </c>
     </row>
     <row r="21" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B21" t="s">
+      <c r="B21" t="s" s="0">
         <v>186</v>
       </c>
     </row>
     <row r="22" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B22" t="s">
+      <c r="B22" t="s" s="0">
         <v>224</v>
       </c>
     </row>
     <row r="23" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B23" t="s">
+      <c r="B23" t="s" s="0">
         <v>225</v>
       </c>
     </row>
     <row r="24" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B24" t="s">
+      <c r="B24" t="s" s="0">
         <v>226</v>
       </c>
     </row>
     <row r="25" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B25" t="s">
+      <c r="B25" t="s" s="0">
         <v>227</v>
       </c>
     </row>
     <row r="26" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B26" t="s">
+      <c r="B26" t="s" s="0">
         <v>228</v>
       </c>
     </row>
     <row r="27" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B27" t="s">
+      <c r="B27" t="s" s="0">
         <v>179</v>
       </c>
     </row>
     <row r="28" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B28" t="s">
+      <c r="B28" t="s" s="0">
         <v>229</v>
       </c>
     </row>
     <row r="29" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B29" t="s">
+      <c r="B29" t="s" s="0">
         <v>184</v>
       </c>
     </row>
     <row r="30" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B30" t="s">
+      <c r="B30" t="s" s="0">
         <v>230</v>
       </c>
     </row>
     <row r="31" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B31" t="s">
+      <c r="B31" t="s" s="0">
         <v>231</v>
       </c>
     </row>
     <row r="32" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B32" t="s">
+      <c r="B32" t="s" s="0">
         <v>232</v>
       </c>
     </row>
     <row r="33" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B33" t="s">
+      <c r="B33" t="s" s="0">
         <v>233</v>
       </c>
     </row>
     <row r="34" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B34" t="s">
+      <c r="B34" t="s" s="0">
         <v>234</v>
       </c>
     </row>
     <row r="35" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B35" t="s">
+      <c r="B35" t="s" s="0">
         <v>235</v>
       </c>
     </row>
     <row r="36" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B36" t="s">
+      <c r="B36" t="s" s="0">
         <v>236</v>
       </c>
     </row>
     <row r="37" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B37" t="s">
+      <c r="B37" t="s" s="0">
         <v>237</v>
       </c>
     </row>
     <row r="38" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B38" t="s">
+      <c r="B38" t="s" s="0">
         <v>238</v>
       </c>
     </row>
     <row r="39" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B39" t="s">
+      <c r="B39" t="s" s="0">
         <v>239</v>
       </c>
     </row>
     <row r="40" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B40" t="s">
+      <c r="B40" t="s" s="0">
         <v>240</v>
       </c>
     </row>
     <row r="41" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B41" t="s">
+      <c r="B41" t="s" s="0">
         <v>234</v>
       </c>
     </row>
     <row r="42" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B42" t="s">
+      <c r="B42" t="s" s="0">
         <v>241</v>
       </c>
     </row>
     <row r="43" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B43" t="s">
+      <c r="B43" t="s" s="0">
         <v>242</v>
       </c>
     </row>
     <row r="44" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B44" t="s">
+      <c r="B44" t="s" s="0">
         <v>243</v>
       </c>
     </row>
     <row r="45" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B45" t="s">
+      <c r="B45" t="s" s="0">
         <v>238</v>
       </c>
     </row>
     <row r="46" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B46" t="s">
+      <c r="B46" t="s" s="0">
         <v>244</v>
       </c>
     </row>
     <row r="47" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B47" t="s">
+      <c r="B47" t="s" s="0">
         <v>245</v>
       </c>
     </row>
     <row r="48" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B48" t="s">
+      <c r="B48" t="s" s="0">
         <v>246</v>
       </c>
     </row>
     <row r="49" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B49" t="s">
+      <c r="B49" t="s" s="0">
         <v>247</v>
       </c>
     </row>
     <row r="50" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B50" t="s">
+      <c r="B50" t="s" s="0">
         <v>187</v>
       </c>
     </row>
     <row r="51" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B51" t="s">
+      <c r="B51" t="s" s="0">
         <v>188</v>
       </c>
     </row>
     <row r="52" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B52" t="s">
+      <c r="B52" t="s" s="0">
         <v>189</v>
       </c>
     </row>
     <row r="53" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B53" t="s">
+      <c r="B53" t="s" s="0">
         <v>248</v>
       </c>
     </row>
     <row r="54" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B54" t="s">
+      <c r="B54" t="s" s="0">
         <v>249</v>
       </c>
     </row>
     <row r="55" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B55" t="s">
+      <c r="B55" t="s" s="0">
         <v>190</v>
       </c>
     </row>
@@ -2626,146 +2640,146 @@
   <dimension ref="B2:L29"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.875" customWidth="1"/>
-    <col min="2" max="2" width="15.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.75" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="16.875"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="15.125"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="24.875"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="23.75"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="C2" t="s">
+      <c r="C2" t="s" s="0">
         <v>214</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" t="s" s="0">
         <v>213</v>
       </c>
     </row>
     <row r="3" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>208</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" t="s" s="0">
         <v>10</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" t="s" s="0">
         <v>196</v>
       </c>
     </row>
     <row r="4" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B4" t="s">
+      <c r="B4" t="s" s="0">
         <v>216</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" t="s" s="0">
         <v>250</v>
       </c>
     </row>
     <row r="5" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B5" t="s">
+      <c r="B5" t="s" s="0">
         <v>263</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" t="s" s="0">
         <v>268</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" t="s" s="0">
         <v>251</v>
       </c>
     </row>
     <row r="6" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B6" t="s">
+      <c r="B6" t="s" s="0">
         <v>270</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" t="s" s="0">
         <v>11</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" t="s" s="0">
         <v>252</v>
       </c>
     </row>
     <row r="7" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B7" t="s">
+      <c r="B7" t="s" s="0">
         <v>267</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" t="s" s="0">
         <v>35</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" t="s" s="0">
         <v>218</v>
       </c>
     </row>
     <row r="8" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B8" t="s">
+      <c r="B8" t="s" s="0">
         <v>269</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" t="s" s="0">
         <v>268</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" t="s" s="0">
         <v>253</v>
       </c>
     </row>
     <row r="9" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B9" t="s">
+      <c r="B9" t="s" s="0">
         <v>209</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" t="s" s="0">
         <v>194</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" t="s" s="0">
         <v>192</v>
       </c>
     </row>
     <row r="10" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B10" t="s">
+      <c r="B10" t="s" s="0">
         <v>210</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" t="s" s="0">
         <v>195</v>
       </c>
     </row>
     <row r="11" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B11" t="s">
+      <c r="B11" t="s" s="0">
         <v>206</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" t="s" s="0">
         <v>268</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11" t="s" s="0">
         <v>198</v>
       </c>
     </row>
     <row r="12" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B12" t="s">
+      <c r="B12" t="s" s="0">
         <v>264</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" t="s" s="0">
         <v>268</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D12" t="s" s="0">
         <v>254</v>
       </c>
     </row>
     <row r="13" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B13" t="s">
+      <c r="B13" t="s" s="0">
         <v>205</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" t="s" s="0">
         <v>37</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D13" t="s" s="0">
         <v>199</v>
       </c>
     </row>
     <row r="14" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B14" t="s">
+      <c r="B14" t="s" s="0">
         <v>265</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" t="s" s="0">
         <v>38</v>
       </c>
       <c r="D14" s="4" t="s">
@@ -2773,10 +2787,10 @@
       </c>
     </row>
     <row r="15" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B15" t="s">
+      <c r="B15" t="s" s="0">
         <v>260</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" t="s" s="0">
         <v>36</v>
       </c>
       <c r="D15" s="4" t="s">
@@ -2784,68 +2798,68 @@
       </c>
     </row>
     <row r="16" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B16" t="s">
+      <c r="B16" t="s" s="0">
         <v>273</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C16" t="s" s="0">
         <v>268</v>
       </c>
-      <c r="D16" t="s">
+      <c r="D16" t="s" s="0">
         <v>256</v>
       </c>
     </row>
     <row r="17" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B17" t="s">
+      <c r="B17" t="s" s="0">
         <v>211</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C17" t="s" s="0">
         <v>23</v>
       </c>
-      <c r="D17" t="s">
+      <c r="D17" t="s" s="0">
         <v>201</v>
       </c>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B18" t="s">
+      <c r="B18" t="s" s="0">
         <v>262</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C18" t="s" s="0">
         <v>16</v>
       </c>
-      <c r="D18" t="s">
+      <c r="D18" t="s" s="0">
         <v>204</v>
       </c>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B19" t="s">
+      <c r="B19" t="s" s="0">
         <v>217</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C19" t="s" s="0">
         <v>6</v>
       </c>
-      <c r="D19" t="s">
+      <c r="D19" t="s" s="0">
         <v>191</v>
       </c>
     </row>
     <row r="20" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B20" t="s">
+      <c r="B20" t="s" s="0">
         <v>212</v>
       </c>
       <c r="C20" s="4" t="s">
         <v>261</v>
       </c>
-      <c r="D20" t="s">
+      <c r="D20" t="s" s="0">
         <v>202</v>
       </c>
     </row>
     <row r="21" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B21" t="s">
+      <c r="B21" t="s" s="0">
         <v>207</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C21" t="s" s="0">
         <v>1</v>
       </c>
-      <c r="D21" t="s">
+      <c r="D21" t="s" s="0">
         <v>197</v>
       </c>
       <c r="E21" s="4"/>
@@ -2858,10 +2872,10 @@
       <c r="L21" s="4"/>
     </row>
     <row r="22" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B22" t="s">
+      <c r="B22" t="s" s="0">
         <v>215</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C22" t="s" s="0">
         <v>4</v>
       </c>
       <c r="D22" s="4" t="s">
@@ -2869,35 +2883,35 @@
       </c>
     </row>
     <row r="23" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B23" t="s">
+      <c r="B23" t="s" s="0">
         <v>271</v>
       </c>
       <c r="C23" s="4" t="s">
         <v>274</v>
       </c>
-      <c r="D23" t="s">
+      <c r="D23" t="s" s="0">
         <v>257</v>
       </c>
     </row>
     <row r="24" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B24" t="s">
+      <c r="B24" t="s" s="0">
         <v>272</v>
       </c>
       <c r="C24" s="4" t="s">
         <v>268</v>
       </c>
-      <c r="D24" t="s">
+      <c r="D24" t="s" s="0">
         <v>258</v>
       </c>
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B25" t="s">
+      <c r="B25" t="s" s="0">
         <v>275</v>
       </c>
       <c r="C25" s="4" t="s">
         <v>276</v>
       </c>
-      <c r="D25" t="s">
+      <c r="D25" t="s" s="0">
         <v>259</v>
       </c>
     </row>
@@ -2911,4 +2925,49 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="24.16015625"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="0">
+        <v>159</v>
+      </c>
+      <c r="B1" t="s" s="0">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>106</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>128</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>280</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
 </file>
--- a/src/main/resources/excel/exceldata.xlsx
+++ b/src/main/resources/excel/exceldata.xlsx
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="411" uniqueCount="281">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="419" uniqueCount="281">
   <si>
     <t>company_id</t>
   </si>

--- a/src/main/resources/excel/exceldata.xlsx
+++ b/src/main/resources/excel/exceldata.xlsx
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="419" uniqueCount="281">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="281">
   <si>
     <t>company_id</t>
   </si>

--- a/src/main/resources/excel/exceldata.xlsx
+++ b/src/main/resources/excel/exceldata.xlsx
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="281">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="451" uniqueCount="281">
   <si>
     <t>company_id</t>
   </si>

--- a/src/main/resources/excel/exceldata.xlsx
+++ b/src/main/resources/excel/exceldata.xlsx
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="451" uniqueCount="281">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="787" uniqueCount="284">
   <si>
     <t>company_id</t>
   </si>
@@ -914,6 +914,15 @@
   </si>
   <si>
     <t>{"data":{"companyInfo":{"contents":{"defenseDesignationDate":"2021-07-06","businessNum":"139-81-08139","defenseRevenue":"","establishmentDate":"1992-07-01","civilianProducts":"소음, 진동, 충격 방지 제품","companyZipCode":"21691","comClassification":"제조업","companySize":"1","companyForm":"3","defenseProducts":"소음, 진동, 충격 방지 제품","homepageUrl":"http://www.nsv.co.kr","companyAddr2Ko":" NSV 사옥","name":"(주)엔에스브이","companyAddr1Ko":"인천 남동구 앵고개로 547 (고잔동)","companyMemberGubun":"G2","ceoName":"윤은중","totalRevenue":"28519","productList":""}}}}</t>
+  </si>
+  <si>
+    <t>SMALL</t>
+  </si>
+  <si>
+    <t>1900.1.1</t>
+  </si>
+  <si>
+    <t>26.02.24</t>
   </si>
 </sst>
 </file>
@@ -2929,10 +2938,21 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" bestFit="true" customWidth="true" width="24.16015625"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="60.0"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="16.0"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="26.0"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="28.0"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="10.0"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="13.0"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" width="14.40234375"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="15.0"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" width="13.0"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" width="13.0"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" width="15.0"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2940,7 +2960,37 @@
         <v>159</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>277</v>
+        <v>160</v>
+      </c>
+      <c r="C1" t="s" s="0">
+        <v>161</v>
+      </c>
+      <c r="D1" t="s" s="0">
+        <v>162</v>
+      </c>
+      <c r="E1" t="s" s="0">
+        <v>163</v>
+      </c>
+      <c r="F1" t="s" s="0">
+        <v>164</v>
+      </c>
+      <c r="G1" t="s" s="0">
+        <v>165</v>
+      </c>
+      <c r="H1" t="s" s="0">
+        <v>166</v>
+      </c>
+      <c r="I1" t="s" s="0">
+        <v>167</v>
+      </c>
+      <c r="J1" t="s" s="0">
+        <v>168</v>
+      </c>
+      <c r="K1" t="s" s="0">
+        <v>169</v>
+      </c>
+      <c r="L1" t="s" s="0">
+        <v>170</v>
       </c>
     </row>
     <row r="2">
@@ -2950,6 +3000,36 @@
       <c r="B2" t="s" s="0">
         <v>278</v>
       </c>
+      <c r="C2" t="s" s="0">
+        <v>281</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>127</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>282</v>
+      </c>
+      <c r="F2" t="s" s="0">
+        <v>98</v>
+      </c>
+      <c r="G2" t="s" s="0">
+        <v>173</v>
+      </c>
+      <c r="H2" t="s" s="0">
+        <v>174</v>
+      </c>
+      <c r="I2" t="s" s="0">
+        <v>283</v>
+      </c>
+      <c r="J2" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="K2" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="L2" t="s" s="0">
+        <v>80</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
@@ -2958,6 +3038,36 @@
       <c r="B3" t="s" s="0">
         <v>279</v>
       </c>
+      <c r="C3" t="s" s="0">
+        <v>281</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>127</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>282</v>
+      </c>
+      <c r="F3" t="s" s="0">
+        <v>98</v>
+      </c>
+      <c r="G3" t="s" s="0">
+        <v>173</v>
+      </c>
+      <c r="H3" t="s" s="0">
+        <v>174</v>
+      </c>
+      <c r="I3" t="s" s="0">
+        <v>283</v>
+      </c>
+      <c r="J3" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="K3" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="L3" t="s" s="0">
+        <v>80</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
@@ -2965,6 +3075,36 @@
       </c>
       <c r="B4" t="s" s="0">
         <v>280</v>
+      </c>
+      <c r="C4" t="s" s="0">
+        <v>281</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>127</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>282</v>
+      </c>
+      <c r="F4" t="s" s="0">
+        <v>98</v>
+      </c>
+      <c r="G4" t="s" s="0">
+        <v>173</v>
+      </c>
+      <c r="H4" t="s" s="0">
+        <v>174</v>
+      </c>
+      <c r="I4" t="s" s="0">
+        <v>283</v>
+      </c>
+      <c r="J4" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="K4" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="L4" t="s" s="0">
+        <v>80</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/excel/exceldata.xlsx
+++ b/src/main/resources/excel/exceldata.xlsx
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="787" uniqueCount="284">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1027" uniqueCount="284">
   <si>
     <t>company_id</t>
   </si>

--- a/src/main/resources/excel/exceldata.xlsx
+++ b/src/main/resources/excel/exceldata.xlsx
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1027" uniqueCount="284">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1075" uniqueCount="284">
   <si>
     <t>company_id</t>
   </si>

--- a/src/main/resources/excel/exceldata.xlsx
+++ b/src/main/resources/excel/exceldata.xlsx
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1075" uniqueCount="284">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1171" uniqueCount="285">
   <si>
     <t>company_id</t>
   </si>
@@ -923,6 +923,9 @@
   </si>
   <si>
     <t>26.02.24</t>
+  </si>
+  <si>
+    <t>26.02.25</t>
   </si>
 </sst>
 </file>
@@ -3019,7 +3022,7 @@
         <v>174</v>
       </c>
       <c r="I2" t="s" s="0">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="J2" t="s" s="0">
         <v>80</v>
@@ -3057,7 +3060,7 @@
         <v>174</v>
       </c>
       <c r="I3" t="s" s="0">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="J3" t="s" s="0">
         <v>80</v>
@@ -3095,7 +3098,7 @@
         <v>174</v>
       </c>
       <c r="I4" t="s" s="0">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="J4" t="s" s="0">
         <v>80</v>

--- a/src/main/resources/excel/exceldata.xlsx
+++ b/src/main/resources/excel/exceldata.xlsx
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1171" uniqueCount="285">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1411" uniqueCount="291">
   <si>
     <t>company_id</t>
   </si>
@@ -926,6 +926,24 @@
   </si>
   <si>
     <t>26.02.25</t>
+  </si>
+  <si>
+    <t>2026-02-25 13:46:34</t>
+  </si>
+  <si>
+    <t>2026-02-25 13:47:04</t>
+  </si>
+  <si>
+    <t>2026-02-25 13:51:51</t>
+  </si>
+  <si>
+    <t>2026-02-25 13:52:18</t>
+  </si>
+  <si>
+    <t>NULL</t>
+  </si>
+  <si>
+    <t>2026-02-25 13:55:22</t>
   </si>
 </sst>
 </file>
@@ -2952,7 +2970,7 @@
     <col min="6" max="6" bestFit="true" customWidth="true" width="10.0"/>
     <col min="7" max="7" bestFit="true" customWidth="true" width="13.0"/>
     <col min="8" max="8" bestFit="true" customWidth="true" width="14.40234375"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" width="15.0"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="18.23046875"/>
     <col min="10" max="10" bestFit="true" customWidth="true" width="13.0"/>
     <col min="11" max="11" bestFit="true" customWidth="true" width="13.0"/>
     <col min="12" max="12" bestFit="true" customWidth="true" width="15.0"/>
@@ -3010,7 +3028,7 @@
         <v>127</v>
       </c>
       <c r="E2" t="s" s="0">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="F2" t="s" s="0">
         <v>98</v>
@@ -3022,7 +3040,7 @@
         <v>174</v>
       </c>
       <c r="I2" t="s" s="0">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="J2" t="s" s="0">
         <v>80</v>
@@ -3048,7 +3066,7 @@
         <v>127</v>
       </c>
       <c r="E3" t="s" s="0">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="F3" t="s" s="0">
         <v>98</v>
@@ -3060,7 +3078,7 @@
         <v>174</v>
       </c>
       <c r="I3" t="s" s="0">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="J3" t="s" s="0">
         <v>80</v>
@@ -3086,7 +3104,7 @@
         <v>127</v>
       </c>
       <c r="E4" t="s" s="0">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="F4" t="s" s="0">
         <v>98</v>
@@ -3098,7 +3116,7 @@
         <v>174</v>
       </c>
       <c r="I4" t="s" s="0">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="J4" t="s" s="0">
         <v>80</v>

--- a/src/main/resources/excel/exceldata.xlsx
+++ b/src/main/resources/excel/exceldata.xlsx
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1411" uniqueCount="291">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1459" uniqueCount="292">
   <si>
     <t>company_id</t>
   </si>
@@ -944,6 +944,9 @@
   </si>
   <si>
     <t>2026-02-25 13:55:22</t>
+  </si>
+  <si>
+    <t>2026-02-25 14:07:48</t>
   </si>
 </sst>
 </file>
@@ -3040,16 +3043,16 @@
         <v>174</v>
       </c>
       <c r="I2" t="s" s="0">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="J2" t="s" s="0">
-        <v>80</v>
+        <v>289</v>
       </c>
       <c r="K2" t="s" s="0">
-        <v>80</v>
+        <v>289</v>
       </c>
       <c r="L2" t="s" s="0">
-        <v>80</v>
+        <v>289</v>
       </c>
     </row>
     <row r="3">
@@ -3078,16 +3081,16 @@
         <v>174</v>
       </c>
       <c r="I3" t="s" s="0">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="J3" t="s" s="0">
-        <v>80</v>
+        <v>289</v>
       </c>
       <c r="K3" t="s" s="0">
-        <v>80</v>
+        <v>289</v>
       </c>
       <c r="L3" t="s" s="0">
-        <v>80</v>
+        <v>289</v>
       </c>
     </row>
     <row r="4">
@@ -3116,16 +3119,16 @@
         <v>174</v>
       </c>
       <c r="I4" t="s" s="0">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="J4" t="s" s="0">
-        <v>80</v>
+        <v>289</v>
       </c>
       <c r="K4" t="s" s="0">
-        <v>80</v>
+        <v>289</v>
       </c>
       <c r="L4" t="s" s="0">
-        <v>80</v>
+        <v>289</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/excel/exceldata.xlsx
+++ b/src/main/resources/excel/exceldata.xlsx
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1459" uniqueCount="292">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1507" uniqueCount="293">
   <si>
     <t>company_id</t>
   </si>
@@ -947,6 +947,9 @@
   </si>
   <si>
     <t>2026-02-25 14:07:48</t>
+  </si>
+  <si>
+    <t>2026-02-25 14:19:30</t>
   </si>
 </sst>
 </file>
@@ -3043,7 +3046,7 @@
         <v>174</v>
       </c>
       <c r="I2" t="s" s="0">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="J2" t="s" s="0">
         <v>289</v>
@@ -3081,7 +3084,7 @@
         <v>174</v>
       </c>
       <c r="I3" t="s" s="0">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="J3" t="s" s="0">
         <v>289</v>
@@ -3119,7 +3122,7 @@
         <v>174</v>
       </c>
       <c r="I4" t="s" s="0">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="J4" t="s" s="0">
         <v>289</v>
